--- a/doc/PRESUPUESTO.xlsx
+++ b/doc/PRESUPUESTO.xlsx
@@ -1,27 +1,154 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\Universidad\S9-MASTER\EMC\MOUNTAIN_IN_THE_POCKET\doc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDF55BA-10DA-4E87-80AE-947CE3B3FFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>COMPONENTE</t>
+  </si>
+  <si>
+    <t>CANTIDAD</t>
+  </si>
+  <si>
+    <t>PRECIO</t>
+  </si>
+  <si>
+    <t>LINK</t>
+  </si>
+  <si>
+    <t>FARNELL</t>
+  </si>
+  <si>
+    <t>SEN0137</t>
+  </si>
+  <si>
+    <t>DESCRIPCIÓN</t>
+  </si>
+  <si>
+    <t>Sensor de temperatura y humedad</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/dfrobot/sen0137/kit-desarr-sensor-humedadtemp/dp/3517874</t>
+  </si>
+  <si>
+    <t>SEN0251</t>
+  </si>
+  <si>
+    <t>Barómetro</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/dfrobot/sen0251/barometric-pressure-sensors-module/dp/3879705</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/wurth-elektronik/157142v12803/pantalla-7seg-nodo-com-n-verde/dp/3779170</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>157142V12803</t>
+  </si>
+  <si>
+    <t>Display 7 segmentos</t>
+  </si>
+  <si>
+    <t>NORPS-12</t>
+  </si>
+  <si>
+    <t>LDR</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/advanced-photonix/norps-12/light-dependent-resistor-1mohm/dp/327700</t>
+  </si>
+  <si>
+    <t>3362P-1-103LF</t>
+  </si>
+  <si>
+    <t>Potenciometro</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/bourns/3362p-1-103lf/pot-trimmer-10k-3-pin/dp/9354301</t>
+  </si>
+  <si>
+    <t>CEM-1206S</t>
+  </si>
+  <si>
+    <t>Buzzer</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/same-sky/cem-1206s/transudct-zumb-mag-92dba-3-8v/dp/4814136</t>
+  </si>
+  <si>
+    <t>Transistor del buzzer</t>
+  </si>
+  <si>
+    <t>Diodo de descarga del buzzer</t>
+  </si>
+  <si>
+    <t>LED indicador</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -37,7 +164,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -45,14 +172,74 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +517,267 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="19.9296875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19.3984375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="28.1328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="5" customWidth="1"/>
+    <col min="5" max="6" width="9.06640625" style="6"/>
+    <col min="7" max="7" width="82.19921875" style="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6">
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="F2" s="6">
+        <f>E2*D2</f>
+        <v>9.2899999999999991</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>7.19</v>
+      </c>
+      <c r="F3" s="6">
+        <f t="shared" ref="F3:F7" si="0">E3*D3</f>
+        <v>7.19</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="F4" s="6">
+        <f t="shared" si="0"/>
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
+        <v>2.23</v>
+      </c>
+      <c r="F5" s="6">
+        <f t="shared" si="0"/>
+        <v>2.23</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" si="0"/>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.1652</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="0"/>
+        <v>1.1652</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G26" s="7"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/doc/PRESUPUESTO.xlsx
+++ b/doc/PRESUPUESTO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\Universidad\S9-MASTER\EMC\MOUNTAIN_IN_THE_POCKET\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDF55BA-10DA-4E87-80AE-947CE3B3FFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42319328-43A8-4F36-AAA8-B4E64CFDACC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>PROVEEDOR</t>
   </si>
@@ -107,22 +107,37 @@
     <t>https://es.farnell.com/bourns/3362p-1-103lf/pot-trimmer-10k-3-pin/dp/9354301</t>
   </si>
   <si>
-    <t>CEM-1206S</t>
-  </si>
-  <si>
     <t>Buzzer</t>
   </si>
   <si>
-    <t>https://es.farnell.com/same-sky/cem-1206s/transudct-zumb-mag-92dba-3-8v/dp/4814136</t>
-  </si>
-  <si>
-    <t>Transistor del buzzer</t>
-  </si>
-  <si>
-    <t>Diodo de descarga del buzzer</t>
-  </si>
-  <si>
     <t>LED indicador</t>
+  </si>
+  <si>
+    <t>Pulsador</t>
+  </si>
+  <si>
+    <t>STLED316SMTR</t>
+  </si>
+  <si>
+    <t>Controlador display 7 segmentos</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/stmicroelectronics/stled316smtr/control-led-keyscan-14-salida/dp/2806851</t>
+  </si>
+  <si>
+    <t>CEM-1205-IC</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/same-sky/cem-1205-ic/transudct-zumb-mag-92dba-3-6v/dp/4814135#anchorTechnicalDOCS</t>
+  </si>
+  <si>
+    <t>Mosfet del buzzer</t>
+  </si>
+  <si>
+    <t>2N7002</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/onsemi/2n7002/mosfet-n-ch-60v-115ma-to-263ab/dp/2323152</t>
   </si>
 </sst>
 </file>
@@ -132,7 +147,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +166,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -210,11 +233,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -237,8 +261,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -593,7 +621,7 @@
         <v>7.19</v>
       </c>
       <c r="F3" s="6">
-        <f t="shared" ref="F3:F7" si="0">E3*D3</f>
+        <f t="shared" ref="F3:F9" si="0">E3*D3</f>
         <v>7.19</v>
       </c>
       <c r="G3" s="7" t="s">
@@ -620,7 +648,7 @@
         <f t="shared" si="0"/>
         <v>4.4800000000000004</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -629,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="6">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6">
-        <f t="shared" si="0"/>
-        <v>2.23</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>19</v>
+        <f>E5*D5</f>
+        <v>2</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -653,23 +681,23 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" s="5">
         <v>1</v>
       </c>
       <c r="E6" s="6">
-        <v>1.1200000000000001</v>
+        <v>2.23</v>
       </c>
       <c r="F6" s="6">
         <f t="shared" si="0"/>
-        <v>1.1200000000000001</v>
+        <v>2.23</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -677,59 +705,83 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D7" s="5">
         <v>1</v>
       </c>
       <c r="E7" s="6">
-        <v>1.1652</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F7" s="6">
         <f t="shared" si="0"/>
-        <v>1.1652</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="C8" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" s="5">
         <v>1</v>
       </c>
-      <c r="G8" s="7"/>
+      <c r="E8" s="6">
+        <v>2.17</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="0"/>
+        <v>2.17</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="C9" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D9" s="5">
         <v>1</v>
       </c>
-      <c r="G9" s="7"/>
+      <c r="E9" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="0"/>
+        <v>2.9</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="5" t="s">
-        <v>5</v>
-      </c>
       <c r="C10" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C11" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
@@ -778,6 +830,10 @@
       <c r="G26" s="7"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G4" r:id="rId1" xr:uid="{60EF82CD-5EF6-4223-B34F-B18CA6194041}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId2"/>
 </worksheet>
 </file>
--- a/doc/PRESUPUESTO.xlsx
+++ b/doc/PRESUPUESTO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\Universidad\S9-MASTER\EMC\MOUNTAIN_IN_THE_POCKET\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42319328-43A8-4F36-AAA8-B4E64CFDACC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B87EA4-355C-43BD-A65D-141DF396BAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="9766" windowHeight="11363" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
   <si>
     <t>PROVEEDOR</t>
   </si>
@@ -138,6 +138,12 @@
   </si>
   <si>
     <t>https://es.farnell.com/onsemi/2n7002/mosfet-n-ch-60v-115ma-to-263ab/dp/2323152</t>
+  </si>
+  <si>
+    <t>Baterías</t>
+  </si>
+  <si>
+    <t>Soporte baterías</t>
   </si>
 </sst>
 </file>
@@ -785,9 +791,15 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C12" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="C13" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">

--- a/doc/PRESUPUESTO.xlsx
+++ b/doc/PRESUPUESTO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\Universidad\S9-MASTER\EMC\MOUNTAIN_IN_THE_POCKET\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B87EA4-355C-43BD-A65D-141DF396BAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAD3864-9378-4162-A66E-6C870D2F42CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="9766" windowHeight="11363" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/doc/PRESUPUESTO.xlsx
+++ b/doc/PRESUPUESTO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Documents\Universidad\S9-MASTER\EMC\MOUNTAIN_IN_THE_POCKET\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAD3864-9378-4162-A66E-6C870D2F42CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16075844-C317-4F58-83AC-8AC770C468A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,9 +77,6 @@
     <t>https://es.farnell.com/dfrobot/sen0251/barometric-pressure-sensors-module/dp/3879705</t>
   </si>
   <si>
-    <t>https://es.farnell.com/wurth-elektronik/157142v12803/pantalla-7seg-nodo-com-n-verde/dp/3779170</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>Controlador display 7 segmentos</t>
   </si>
   <si>
-    <t>https://es.farnell.com/stmicroelectronics/stled316smtr/control-led-keyscan-14-salida/dp/2806851</t>
-  </si>
-  <si>
     <t>CEM-1205-IC</t>
   </si>
   <si>
@@ -144,6 +138,12 @@
   </si>
   <si>
     <t>Soporte baterías</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/ams-osram-group/as1115-bsst/display-driver-40-to-125deg-c/dp/4328186RL</t>
+  </si>
+  <si>
+    <t>https://es.farnell.com/wurth-elektronik/157142s12703/pantalla-7seg-c-todo-com-n-s-per/dp/3779167?utm_source=chatgpt.com</t>
   </si>
 </sst>
 </file>
@@ -580,7 +580,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>4</v>
@@ -639,23 +639,23 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>16</v>
       </c>
       <c r="D4" s="5">
         <v>4</v>
       </c>
       <c r="E4" s="6">
-        <v>1.1200000000000001</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="F4" s="6">
         <f t="shared" si="0"/>
-        <v>4.4800000000000004</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
@@ -663,23 +663,23 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="6">
-        <v>2</v>
+        <v>3.18</v>
       </c>
       <c r="F5" s="6">
         <f>E5*D5</f>
-        <v>2</v>
+        <v>3.18</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
@@ -687,10 +687,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="D6" s="5">
         <v>1</v>
@@ -703,7 +703,7 @@
         <v>2.23</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
@@ -711,10 +711,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="D7" s="5">
         <v>1</v>
@@ -727,7 +727,7 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
@@ -735,10 +735,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="5">
         <v>1</v>
@@ -751,7 +751,7 @@
         <v>2.17</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -759,10 +759,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D9" s="5">
         <v>1</v>
@@ -775,30 +775,30 @@
         <v>2.9</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C11" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C12" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C13" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G13" s="7"/>
     </row>
@@ -843,7 +843,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G4" r:id="rId1" xr:uid="{60EF82CD-5EF6-4223-B34F-B18CA6194041}"/>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{81C6D64D-54DA-4037-9E96-134E25B37A9D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId2"/>
